--- a/Content/Labs/cmetingenmateriaal.xlsx
+++ b/Content/Labs/cmetingenmateriaal.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2DD36FB-F072-4E90-95E4-C47FFA32E384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\Documents\Studie\TN Eerste jaar\Inleidendpracticum2\thermolab_MatthijsvOostrum_BenGeertman_groepje_3.5\Content\Labs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C264FFE-BE01-41BD-93DE-26F11BE52287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>dTw</t>
   </si>
@@ -48,41 +53,14 @@
     <t>Theetwater</t>
   </si>
   <si>
-    <t>2.8</t>
-  </si>
-  <si>
-    <t>21.0</t>
-  </si>
-  <si>
-    <t>68.5</t>
-  </si>
-  <si>
     <t>Twb = 21.0</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t>199.32</t>
-  </si>
-  <si>
-    <t>20.8</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>21.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,17 +439,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.1328125" customWidth="1"/>
+    <col min="4" max="4" width="23.86328125" customWidth="1"/>
+    <col min="5" max="5" width="27.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,58 +466,126 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>2.8</v>
+      </c>
+      <c r="B2">
+        <v>300</v>
+      </c>
+      <c r="C2">
+        <v>300</v>
+      </c>
+      <c r="D2">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <v>68.5</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>300</v>
-      </c>
-      <c r="C2">
-        <v>300</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>9</v>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>3.4</v>
       </c>
       <c r="B3">
         <v>300</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>12</v>
+      <c r="C3">
+        <v>199.32</v>
+      </c>
+      <c r="D3">
+        <v>20.8</v>
+      </c>
+      <c r="E3">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>0.3</v>
       </c>
       <c r="B4">
         <v>305</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="C4">
+        <v>50.3</v>
+      </c>
+      <c r="D4">
+        <v>21.1</v>
+      </c>
+      <c r="E4">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>2.9</v>
+      </c>
+      <c r="B5">
+        <v>300</v>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>20.9</v>
+      </c>
+      <c r="E5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>4.2</v>
+      </c>
+      <c r="B6">
+        <v>300</v>
+      </c>
+      <c r="C6">
+        <v>250</v>
+      </c>
+      <c r="D6">
+        <v>21.2</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>300</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7">
+        <v>20.8</v>
+      </c>
+      <c r="E7">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B8">
+        <v>300</v>
+      </c>
+      <c r="C8">
+        <v>300</v>
+      </c>
+      <c r="D8">
+        <v>24.6</v>
+      </c>
+      <c r="E8">
+        <v>70.099999999999994</v>
       </c>
     </row>
   </sheetData>
